--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G11">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G16">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>3.28</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q5">
         <v>3.6</v>
       </c>
       <c r="R5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
         <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="V5">
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA5">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
         <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
         <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AK5">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
         <v>0</v>

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="O5">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="P5">
         <v>2.31</v>
@@ -1154,34 +1154,34 @@
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB5">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC5">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
         <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AK5">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1139,19 +1139,19 @@
         <v>2</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U5">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V5">
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1169,19 +1169,19 @@
         <v>1.73</v>
       </c>
       <c r="AC5">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD5">
         <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
         <v>1.34</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q6">
         <v>0</v>

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-13 21:00:00</t>
+          <t>2026-08-13 21:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G11">
@@ -2205,821 +2205,6 @@
         <v>0</v>
       </c>
       <c r="AU11" t="inlineStr">
-        <is>
-          <t>2026-08-13 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Kapaz</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Sabah</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2026-08-13 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Qarabağ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>İnter Bakı</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
-      <c r="AN13">
-        <v>-1</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>-1</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2026-08-13 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sumqayıt</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Neftçi</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2026-08-13 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Deportes Santa Cruz</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N15">
-        <v>1.81</v>
-      </c>
-      <c r="O15">
-        <v>3.4</v>
-      </c>
-      <c r="P15">
-        <v>3.7</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>-1</v>
-      </c>
-      <c r="AN15">
-        <v>-1</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>-1</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2026-08-13 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Copiapó</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>-1</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
         <is>
           <t>2026-08-13 21:30:00</t>
         </is>

--- a/jogos_2026-08-13.xlsx
+++ b/jogos_2026-08-13.xlsx
@@ -1124,46 +1124,46 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="O5">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="P5">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA5">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
         <v>1.73</v>
@@ -1172,16 +1172,16 @@
         <v>3.8</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>12.8</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>6.33</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>12.1</v>
+        <v>5.24</v>
       </c>
       <c r="O7">
-        <v>6.29</v>
+        <v>3.82</v>
       </c>
       <c r="P7">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL7">
         <v>0</v>
